--- a/public/exports/29188947.xlsx
+++ b/public/exports/29188947.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:O120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,53 +101,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Adelgade 119B</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">5443136</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>839</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,53 +176,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bredgade 64</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">5485</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">2674061</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>350</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,53 +251,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bryggerivej 2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">2667557</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>821</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,53 +326,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bryggerivej 20</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">2667553</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>1472</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,53 +401,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyvelvænget 12A</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">733060, 9428423</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>488</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,53 +476,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kristianslundsvej 2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">9428394</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>1728</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,53 +551,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kristianslundsvej 2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">9428394</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>1195</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,53 +626,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kristianslundsvej 2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">9428394</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>799</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,53 +701,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lindebjerg 40</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">5474</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">2681328</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>320</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -676,53 +776,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sejlerkajen 4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">733028, 5443483</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">39</t>
         </is>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>356</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -741,53 +851,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sejlerkajen 5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">733021, 5443483</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
         </is>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>309</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -806,53 +926,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Torupvej 59</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">5485</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">100068509</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>843</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -871,53 +1001,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Torupvej 59</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">5485</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">100068509</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>417</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -936,53 +1076,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ullerupvænget 2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">2679200</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>255</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1001,53 +1151,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestre Havnevej 11B</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">733005, 5443483</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">55</t>
         </is>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>308</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1066,53 +1226,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestre Havnevej 11C</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">733005, 5443483</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>478</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,53 +1301,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestre Havnevej 15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">733055, 5443483</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">45</t>
         </is>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>292</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1196,53 +1376,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestre Havnevej 29A</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">733090, 5443483</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
         </is>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>260</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1261,53 +1451,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestre Havnevej 29B</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">5443483</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">48</t>
         </is>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>270</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1326,53 +1526,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 24A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2678883</t>
+          <t xml:space="preserve">Ørkebyvej 11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H21">
-        <v>408</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9432842</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J21">
+        <v>396</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 24B</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Østergade 24A</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">2678883</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H22">
-        <v>423</v>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J22">
+        <v>408</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Havnevej 1</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">733030, 5443483</t>
+          <t xml:space="preserve">Østergade 24B</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
-        </is>
-      </c>
-      <c r="H23">
-        <v>432</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2678883</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J23">
+        <v>423</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Havnevej 41</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Østre Havnevej 1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">733006, 5443483</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52</t>
-        </is>
-      </c>
-      <c r="H24">
-        <v>305</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">733030, 5443483</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t xml:space="preserve">76</t>
+        </is>
+      </c>
+      <c r="J24">
+        <v>432</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordmarksvej 8</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9579261</t>
+          <t xml:space="preserve">Østre Havnevej 41</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H25">
-        <v>363</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">733006, 5443483</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013236</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alectia A/S</t>
-        </is>
+          <t xml:space="preserve">52</t>
+        </is>
+      </c>
+      <c r="J25">
+        <v>305</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-04</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldensteensvej 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9428421</t>
+          <t xml:space="preserve">Nordmarksvej 8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="H26">
-        <v>417</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9579261</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030526</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J26">
+        <v>363</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200012725</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Alectia A/S</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-04-20</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019-04-22</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintevej 48B</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldensteensvej 2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">733061, 2671341</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="H27">
-        <v>252</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9428421</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035988</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="J27">
+        <v>417</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-27</t>
+          <t xml:space="preserve">200030526</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alectia A/S</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-04-20</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Havnevej 9A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klintevej 48B</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">733004, 5443483</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49</t>
-        </is>
-      </c>
-      <c r="H28">
-        <v>439</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">733061, 2671341</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">100273550</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Botjek Odense</t>
-        </is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J28">
+        <v>252</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">200035988</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-27</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Havnevej 9C</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vestre Havnevej 9A</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">733004, 5443483</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57</t>
-        </is>
-      </c>
-      <c r="H29">
-        <v>301</v>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t xml:space="preserve">49</t>
+        </is>
+      </c>
+      <c r="J29">
+        <v>439</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">100273550</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Botjek Odense</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupvænget 4</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">734055, 2679200</t>
+          <t xml:space="preserve">Vestre Havnevej 9C</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H30">
-        <v>798</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">733004, 5443483</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311062535</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rådgivende Ingeniørfirma FRI Rævdal ApS</t>
-        </is>
+          <t xml:space="preserve">57</t>
+        </is>
+      </c>
+      <c r="J30">
+        <v>301</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-01</t>
+          <t xml:space="preserve">100273550</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Odense</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022-06-29</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlerkajen 8A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">733038, 5443483</t>
+          <t xml:space="preserve">Ullerupvænget 4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
-        </is>
-      </c>
-      <c r="H31">
-        <v>420</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734055, 2679200</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311130937</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rådgivende Ingenørfirma Rævdal ApS</t>
-        </is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J31">
+        <v>798</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-25</t>
+          <t xml:space="preserve">311062535</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådgivende Ingeniørfirma FRI Rævdal ApS</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-07-01</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2041,55 +2351,65 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalene 42</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2673824</t>
+          <t xml:space="preserve">Sejlerkajen 8A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H32">
-        <v>849</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">733038, 5443483</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559847</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+          <t xml:space="preserve">51</t>
+        </is>
+      </c>
+      <c r="J32">
+        <v>420</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-04</t>
+          <t xml:space="preserve">311130937</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Rådgivende Ingenørfirma Rævdal ApS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2025-08-25</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogsbølle Bygade 54</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dalene 42</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2672618</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H33">
-        <v>4566</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2673824</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559892</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J33">
+        <v>849</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve">311559847</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-04</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Krogsbølle Bygade 54</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2667622</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H34">
-        <v>1910</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2672618</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559888</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J34">
+        <v>4566</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311559892</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-04</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugårdsvej 729</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682126</t>
+          <t xml:space="preserve">Odensevej 8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2679206</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H35">
-        <v>1952</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311559969</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35">
+        <v>718</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311559846</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-11-05</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-11-04</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugårdsvej 729</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682126</t>
+          <t xml:space="preserve">Søndergade 2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H36">
-        <v>1810</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2667622</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559969</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J36">
+        <v>1910</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-05</t>
+          <t xml:space="preserve">311559888</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-11-04</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rugårdsvej 729</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">5462</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">2682126</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H37">
-        <v>966</v>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J37">
+        <v>1952</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">311559969</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rugårdsvej 729</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">5462</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">2682126</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H38">
-        <v>971</v>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J38">
+        <v>1810</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">311559969</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2496,53 +2876,63 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rugårdsvej 729</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">5462</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">2682126</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H39">
-        <v>616</v>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J39">
+        <v>966</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">311559969</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2561,53 +2951,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rugårdsvej 729</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">5462</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">2682126</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H40">
-        <v>794</v>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J40">
+        <v>971</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">311559969</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2626,53 +3026,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedestræde 7</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2677300</t>
+          <t xml:space="preserve">Rugårdsvej 729</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H41">
-        <v>907</v>
+          <t xml:space="preserve">5462</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2682126</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587113</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
-        </is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J41">
+        <v>616</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">311559969</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-11-05</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2691,53 +3101,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedestræde 7</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2677300</t>
+          <t xml:space="preserve">Rugårdsvej 729</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H42">
-        <v>1052</v>
+          <t xml:space="preserve">5462</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2682126</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587113</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
-        </is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J42">
+        <v>794</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">311559969</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-11-05</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2756,53 +3176,63 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frugthaven 16</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928092</t>
+          <t xml:space="preserve">Smedestræde 7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2677300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H43">
-        <v>842</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311647743</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43">
+        <v>907</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311587117</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-10-06</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-03-22</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2821,53 +3251,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 10</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679757</t>
+          <t xml:space="preserve">Smedestræde 7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H44">
-        <v>518</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2677300</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645746</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J44">
+        <v>1052</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311587117</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-10-06</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-03-22</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2886,53 +3326,63 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsebækvej 25A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669671</t>
+          <t xml:space="preserve">Frugthaven 16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H45">
-        <v>2233</v>
+          <t xml:space="preserve">5462</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9928092</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645761</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J45">
+        <v>842</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311647743</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-11-29</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-10-06</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2951,53 +3401,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsebækvej 25A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669671</t>
+          <t xml:space="preserve">Mejerivej 10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H46">
-        <v>627</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2679757</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645764</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J46">
+        <v>518</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311645746</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-11-29</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-10-06</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3016,53 +3476,63 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupvænget 10</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679193</t>
+          <t xml:space="preserve">Horsebækvej 25A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H47">
-        <v>3903</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2669671</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674603</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J47">
+        <v>2233</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311645761</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-04-19</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-11-29</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,53 +3551,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmus Nielsensvej 14</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2678976</t>
+          <t xml:space="preserve">Horsebækvej 25A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H48">
-        <v>360</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2669671</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678244</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J48">
+        <v>627</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311645764</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-05-03</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-11-29</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3146,53 +3626,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kristianslundsvej 4</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2677770</t>
+          <t xml:space="preserve">Ullerupvænget 10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2679193</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H49">
-        <v>678</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311683985</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49">
+        <v>3903</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311674603</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-05-30</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-04-19</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3211,53 +3701,63 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odensevej 8</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmus Nielsensvej 14</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2679206</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2678976</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H50">
-        <v>718</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311683987</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="J50">
+        <v>360</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-30</t>
+          <t xml:space="preserve">311678244</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-05-03</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3276,53 +3776,63 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2667415</t>
+          <t xml:space="preserve">Kristianslundsvej 4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H51">
-        <v>8954</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2677770</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683947</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J51">
+        <v>678</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683985</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3341,53 +3851,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 14</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2667415</t>
+          <t xml:space="preserve">Nordmarksvej 2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H52">
-        <v>455</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2679197</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683950</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J52">
+        <v>7568</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683964</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3406,53 +3926,63 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 5</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skolegade 12</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2665851</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2667415</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H53">
-        <v>700</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311683982</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53">
+        <v>8954</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683947</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3471,53 +4001,63 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgyden 60</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skolegade 14</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7848414</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H54">
-        <v>3272</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2667415</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683961</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J54">
+        <v>455</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683950</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3536,53 +4076,63 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedel Simonsensvej 31</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5474</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681352</t>
+          <t xml:space="preserve">Skolevænget 5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665851</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H55">
-        <v>2531</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311683979</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55">
+        <v>700</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683982</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3601,53 +4151,63 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejruphuse 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2675544</t>
+          <t xml:space="preserve">Skovgyden 60</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7848414</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H56">
-        <v>3047</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311683978</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56">
+        <v>3272</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683961</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3666,53 +4226,63 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 5</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7514995</t>
+          <t xml:space="preserve">Vedel Simonsensvej 31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t xml:space="preserve">5474</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2681352</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H57">
-        <v>2372</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311687071</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57">
+        <v>2531</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683979</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-06-12</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-05-30</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,53 +4301,63 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 5</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vejruphuse 2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7514995</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H58">
-        <v>555</v>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2675544</t>
+        </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311687071</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J58">
+        <v>3047</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311683978</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-06-12</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-05-30</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3796,53 +4376,63 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestergade 5</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">7514995</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H59">
-        <v>1159</v>
-      </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J59">
+        <v>2372</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">311687071</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3861,53 +4451,63 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adamsminde 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5462</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9579337</t>
+          <t xml:space="preserve">Vestergade 5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H60">
-        <v>885</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7514995</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690136</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J60">
+        <v>555</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311687071</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-06-23</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-06-12</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3926,53 +4526,63 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 6</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668390</t>
+          <t xml:space="preserve">Vestergade 5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H61">
-        <v>945</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7514995</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690554</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J61">
+        <v>1159</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311687071</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-06-26</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-06-12</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3991,53 +4601,63 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 8</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668390</t>
+          <t xml:space="preserve">Adamsminde 2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H62">
-        <v>515</v>
+          <t xml:space="preserve">5462</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9579337</t>
+        </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690556</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J62">
+        <v>885</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311690136</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-06-26</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-06-23</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4056,53 +4676,63 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindebjerg 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5474</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681123</t>
+          <t xml:space="preserve">Søndergade 6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668390</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H63">
-        <v>324</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311699662</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63">
+        <v>945</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311690554</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-08-14</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-06-26</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4121,53 +4751,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldensteensvej 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5443453</t>
+          <t xml:space="preserve">Søndergade 8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H64">
-        <v>574</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668390</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703074</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J64">
+        <v>515</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311690556</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-08-28</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-06-26</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4186,53 +4826,63 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldensteensvej 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5443453</t>
+          <t xml:space="preserve">Lindebjerg 2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t xml:space="preserve">5474</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2681123</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H65">
-        <v>281</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311703072</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65">
+        <v>324</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311699662</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-08-28</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-08-14</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4251,53 +4901,63 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">5443453</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H66">
-        <v>1069</v>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703072</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J66">
+        <v>574</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703074</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4316,53 +4976,63 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">5443453</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H67">
-        <v>1232</v>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J67">
+        <v>281</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">311703072</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,53 +5051,63 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9428421</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="H68">
-        <v>528</v>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5443453</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703052</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J68">
+        <v>1069</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703072</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4446,53 +5126,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9428421</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H69">
-        <v>1316</v>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5443453</t>
+        </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703069</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J69">
+        <v>1232</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703072</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4511,53 +5201,63 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">9428421</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="H70">
-        <v>3337</v>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703065</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="J70">
+        <v>528</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703052</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4576,53 +5276,63 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsebækvej 21</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669673</t>
+          <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H71">
-        <v>321</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9428421</t>
+        </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703079</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J71">
+        <v>1316</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703069</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4641,53 +5351,63 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsebækvej 23</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669675</t>
+          <t xml:space="preserve">Gyldensteensvej 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H72">
-        <v>557</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9428421</t>
+        </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703080</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="J72">
+        <v>3337</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703065</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4706,53 +5426,63 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsebækvej 97</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horsebækvej 21</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2662344</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2669673</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H73">
-        <v>1417</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311703061</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="J73">
+        <v>321</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve">311703079</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-28</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4771,53 +5501,63 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 16A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9862158</t>
+          <t xml:space="preserve">Horsebækvej 23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2669675</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H74">
-        <v>800</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311709990</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74">
+        <v>557</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703080</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-09-25</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-08-28</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4836,53 +5576,63 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggerivej 31</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horsebækvej 97</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2668637</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2662344</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H75">
-        <v>260</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311713813</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75">
+        <v>1417</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311703064</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-10-10</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-08-28</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4901,53 +5651,63 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 7</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668228</t>
+          <t xml:space="preserve">Vestergade 16A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9862158</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H76">
-        <v>1280</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311713806</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76">
+        <v>800</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311709990</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-10-10</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-09-25</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4966,53 +5726,63 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspladsen 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bryggerivej 31</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2668146</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668637</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H77">
-        <v>2691</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311717079</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77">
+        <v>260</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311713813</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-10-24</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-10-10</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,53 +5801,63 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 24</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9961576</t>
+          <t xml:space="preserve">Fabriksvej 7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H78">
-        <v>552</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668228</t>
+        </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717066</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J78">
+        <v>1280</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311713806</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-10-24</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-10-10</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5096,53 +5876,63 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 27</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7877121</t>
+          <t xml:space="preserve">Rådhuspladsen 2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668146</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H79">
-        <v>343</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311720258</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79">
+        <v>2691</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311717079</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-11-06</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-10-24</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5161,53 +5951,63 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 8</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9215105</t>
+          <t xml:space="preserve">Vestergade 24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H80">
-        <v>2743</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9961576</t>
+        </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720255</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J80">
+        <v>552</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311717066</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-11-06</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-10-24</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5226,53 +6026,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æbeløgade 2A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5443441</t>
+          <t xml:space="preserve">Vesterled 27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7877121</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H81">
-        <v>325</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311725226</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81">
+        <v>343</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311720258</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-11-28</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-11-06</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5291,53 +6101,63 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 23</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5443434</t>
+          <t xml:space="preserve">Vesterled 8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9215105</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H82">
-        <v>1986</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311725224</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82">
+        <v>2743</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311720255</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-11-28</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-11-06</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5356,53 +6176,63 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebyende 20</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680253</t>
+          <t xml:space="preserve">Æbeløgade 2A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H83">
-        <v>937</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5443441</t>
+        </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725863</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J83">
+        <v>325</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311725226</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-11-30</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-11-28</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5421,53 +6251,63 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordmarksvej 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679197</t>
+          <t xml:space="preserve">Østergade 23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5443434</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H84">
-        <v>7568</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311730032</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="J84">
+        <v>1986</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-19</t>
+          <t xml:space="preserve">311725224</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-11-28</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5486,53 +6326,63 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallundvej 20</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Langebyende 20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2679467</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H85">
-        <v>475</v>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680253</t>
+        </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730855</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J85">
+        <v>937</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311725863</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2033-12-21</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-11-30</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5551,53 +6401,63 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldensteensvej 24</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9428421</t>
+          <t xml:space="preserve">Dallundvej 20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="H86">
-        <v>305</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2679467</t>
+        </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730860</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J86">
+        <v>475</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311730855</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5616,53 +6476,63 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupvænget 1</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9579261</t>
+          <t xml:space="preserve">Gyldensteensvej 24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H87">
-        <v>333</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9428421</t>
+        </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730861</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="J87">
+        <v>305</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311730860</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,53 +6551,63 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 4</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9428421</t>
+          <t xml:space="preserve">Ullerupvænget 1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="H88">
-        <v>364</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9579261</t>
+        </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311732720</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J88">
+        <v>333</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311730861</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-01-11</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2033-12-21</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5746,53 +6626,63 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bogensevej 16</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2674713</t>
+          <t xml:space="preserve">Poppelvej 4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H89">
-        <v>1694</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9428421</t>
+        </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736508</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J89">
+        <v>364</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311732720</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-02-01</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-01-11</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5811,53 +6701,63 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervænget 21</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8278855</t>
+          <t xml:space="preserve">Bogensevej 16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H90">
-        <v>861</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2674713</t>
+        </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737025</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J90">
+        <v>1694</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311736513</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-02-05</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-02-01</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5876,53 +6776,63 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 4</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668390</t>
+          <t xml:space="preserve">Vestervænget 21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H91">
-        <v>513</v>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8278855</t>
+        </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744504</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J91">
+        <v>861</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">311737025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-02-05</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5941,53 +6851,63 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5471</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680157</t>
+          <t xml:space="preserve">Søndergade 4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H92">
-        <v>788</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668390</t>
+        </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746263</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
-        </is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J92">
+        <v>513</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-19</t>
+          <t xml:space="preserve">311744504</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-03-12</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6006,53 +6926,63 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 7</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrivej 2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2680200</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680157</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H93">
-        <v>573</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311746261</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93">
+        <v>788</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311746263</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6071,53 +7001,63 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 59</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vesterled 7</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2678358</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680200</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H94">
-        <v>907</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311750218</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94">
+        <v>573</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311746261</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-04-08</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-03-19</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6136,53 +7076,63 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8242228</t>
+          <t xml:space="preserve">Vestergade 59</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t xml:space="preserve">5471</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2678358</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H95">
-        <v>374</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311750552</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95">
+        <v>907</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311750218</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-04-09</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-04-08</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6201,53 +7151,63 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlerkajen 3</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrivej 2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286842, 286843</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8242228</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H96">
-        <v>668</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311751168</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96">
+        <v>374</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311750552</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-04-11</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-04-09</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6266,53 +7226,63 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 5B</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100031947</t>
+          <t xml:space="preserve">Sejlerkajen 3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286842, 286843</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H97">
-        <v>267</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311753581</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97">
+        <v>668</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311751168</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-04-22</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-04-11</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6331,53 +7301,63 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 1</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabriksvej 5B</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9473003</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100031947</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H98">
-        <v>428</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311758991</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rævdal ApS</t>
-        </is>
+      <c r="J98">
+        <v>267</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-14</t>
+          <t xml:space="preserve">311753581</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rævdal ApS, Rådg. Ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-04-22</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6396,53 +7376,63 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 104</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t xml:space="preserve">9473003</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H99">
-        <v>725</v>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758996</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J99">
+        <v>428</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311758991</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6461,53 +7451,63 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 124</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 104</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t xml:space="preserve">9473003</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H100">
+      <c r="I100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J100">
         <v>725</v>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t xml:space="preserve">311758996</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6526,53 +7526,63 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 144</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 124</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t xml:space="preserve">9473003</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="H101">
+      <c r="I101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J101">
         <v>725</v>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t xml:space="preserve">311758996</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6591,53 +7601,63 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 144</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8505555</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H102">
-        <v>670</v>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9473003</t>
+        </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758988</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="J102">
+        <v>725</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311758996</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6656,53 +7676,63 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ved Kæret 2</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t xml:space="preserve">8505555</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H103">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J103">
         <v>670</v>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311758988</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311758990</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6721,53 +7751,63 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ved Kæret 2</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t xml:space="preserve">8505555</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H104">
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J104">
         <v>670</v>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311758988</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311758990</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6786,53 +7826,63 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 64</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9473003</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8505555</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H105">
-        <v>725</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311758996</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="J105">
+        <v>670</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311758990</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6851,53 +7901,63 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kæret 84</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 64</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t xml:space="preserve">9473003</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H106">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J106">
         <v>725</v>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t xml:space="preserve">311758996</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-14</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6916,53 +7976,63 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 16A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved Kæret 84</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
           <t xml:space="preserve">5450</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2667553</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H107">
-        <v>2698</v>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9473003</t>
+        </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762327</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J107">
+        <v>725</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-28</t>
+          <t xml:space="preserve">311758996</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rævdal ApS</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-05-14</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6981,53 +8051,63 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harritslevvej 7A</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100015855</t>
+          <t xml:space="preserve">Stadionvej 16A</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H108">
-        <v>783</v>
+          <t xml:space="preserve">5450</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2667553</t>
+        </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766864</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J108">
+        <v>2698</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311762327</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2034-06-17</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2034-05-28</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7046,53 +8126,63 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehaven 1</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harritslevvej 7A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t xml:space="preserve">100015855</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H109">
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J109">
         <v>783</v>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311766864</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K109" t="inlineStr">
         <is>
+          <t xml:space="preserve">311766879</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rævdal ApS</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7111,53 +8201,63 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehaven 2</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Møllehaven 1</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t xml:space="preserve">100015855</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H110">
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J110">
         <v>783</v>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311766864</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K110" t="inlineStr">
         <is>
+          <t xml:space="preserve">311766879</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rævdal ApS</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7176,53 +8276,63 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehaven 23</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Møllehaven 2</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t xml:space="preserve">100015855</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H111">
+      <c r="I111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J111">
         <v>783</v>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311766864</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K111" t="inlineStr">
         <is>
+          <t xml:space="preserve">311766879</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rævdal ApS</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7241,53 +8351,63 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehaven 26</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Møllehaven 23</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t xml:space="preserve">100015855</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H112">
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J112">
         <v>783</v>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311766864</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K112" t="inlineStr">
         <is>
+          <t xml:space="preserve">311766879</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rævdal ApS</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7306,53 +8426,63 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørkebyvej 11</t>
+          <t xml:space="preserve">Nordfyns Kommune</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5450</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9432842</t>
+          <t xml:space="preserve">Møllehaven 26</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H113">
-        <v>396</v>
+          <t xml:space="preserve">5400</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100015855</t>
+        </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766853</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J113">
+        <v>783</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311766879</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7371,53 +8501,63 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">Harritslevvej 9</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t xml:space="preserve">100015855</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="H114">
+      <c r="J114">
         <v>1344</v>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t xml:space="preserve">311768999</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-25</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7436,53 +8576,63 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordmarksvej 8</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t xml:space="preserve">9579261</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="H115">
+      <c r="J115">
         <v>1002</v>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t xml:space="preserve">311814123</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimanden ApS</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-26</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7501,53 +8651,63 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">Møllerled 60</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">5400</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t xml:space="preserve">2677300</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H116">
+      <c r="J116">
         <v>531</v>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t xml:space="preserve">311843083</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-04</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7566,53 +8726,63 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lindebjerg 40A</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">5474</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t xml:space="preserve">734058, 2681328</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H117">
+      <c r="J117">
         <v>1366</v>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t xml:space="preserve">311844098</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-10</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7631,53 +8801,63 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ullerupvænget 4</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t xml:space="preserve">734055, 2679200</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>2485</v>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t xml:space="preserve">311844096</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-10</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="N118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7696,53 +8876,63 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ullerupvænget 4</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t xml:space="preserve">734055, 2679200</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>1159</v>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t xml:space="preserve">311844096</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-10</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7761,59 +8951,69 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordfyns Kommune</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ullerupvænget 6</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">5471</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t xml:space="preserve">2679193</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="H120">
+      <c r="J120">
         <v>710</v>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t xml:space="preserve">311902853</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Rævdal ApS</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="N120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M120"/>
+  <autoFilter ref="A1:O120"/>
 </worksheet>
 </file>
--- a/public/exports/29188947.xlsx
+++ b/public/exports/29188947.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
